--- a/report_forms/024_quality_nonconformance_summary_report--report_forms.xlsx
+++ b/report_forms/024_quality_nonconformance_summary_report--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1053,8 +1053,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'material'}</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Material'}</t>
+          <t>Material</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'process'}</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Process'}</t>
+          <t>Process</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Major'}</t>
+          <t>Major</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'informational'}</t>
+          <t>informational</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Informational'}</t>
+          <t>Informational</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'draft'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Draft'}</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
